--- a/InputData/bldgs/BFoCSbQL/BAU Frac of Components Sold by Quality Lvl.xlsx
+++ b/InputData/bldgs/BFoCSbQL/BAU Frac of Components Sold by Quality Lvl.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI\InputData\bldgs\BFoCSbQL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://civicexchangeorg.sharepoint.com/sites/HongKong2050isNowTeamsite/Shared Documents/12 Hong Kong EPS technical note/HK EPS update/eps-us-3.4.7 working/InputData/bldgs/BFoCSbQL/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_37C473D0C9FB14146458E081EA2DDA434D37B491" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6EB16E2-1A65-5348-990E-FF9603DF198B}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="20115" windowHeight="9780"/>
+    <workbookView xWindow="120" yWindow="500" windowWidth="25660" windowHeight="16420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,12 +19,25 @@
     <sheet name="BFoCSbQL-rural-residential" sheetId="5" r:id="rId4"/>
     <sheet name="BFoCSbQL-commercial" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="83">
   <si>
     <t>Source:</t>
   </si>
@@ -266,12 +280,18 @@
   </si>
   <si>
     <t>for energy efficient rebates.</t>
+  </si>
+  <si>
+    <t>Note by Wing 300823</t>
+  </si>
+  <si>
+    <t>The Data Book has not been updated since 2011.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -350,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -371,16 +391,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -400,9 +415,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -440,9 +455,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -477,7 +492,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -512,7 +527,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -685,20 +700,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="54.28515625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,54 +721,64 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2012</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -763,44 +788,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="59.85546875" customWidth="1"/>
+    <col min="3" max="3" width="23.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="59.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -820,7 +845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -840,7 +865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
@@ -857,7 +882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -874,7 +899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
         <v>18</v>
@@ -892,45 +917,44 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="2">
         <v>3519000</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="2">
         <v>0.27</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="2">
         <v>1652000</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="2">
         <v>0.46</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>14</v>
@@ -948,7 +972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>2</v>
       </c>
@@ -968,7 +992,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -989,7 +1013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>27</v>
       </c>
@@ -1007,7 +1031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>28</v>
       </c>
@@ -1025,7 +1049,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1045,7 +1069,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -1062,7 +1086,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>36</v>
       </c>
@@ -1079,7 +1103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>40</v>
       </c>
@@ -1096,7 +1120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>41</v>
       </c>
@@ -1113,7 +1137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>42</v>
       </c>
@@ -1130,7 +1154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>33</v>
       </c>
@@ -1147,7 +1171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
         <v>35</v>
@@ -1165,7 +1189,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -1185,7 +1209,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>45</v>
       </c>
@@ -1202,7 +1226,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>46</v>
       </c>
@@ -1219,7 +1243,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>47</v>
       </c>
@@ -1236,7 +1260,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>48</v>
       </c>
@@ -1253,7 +1277,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1274,7 +1298,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>56</v>
       </c>
@@ -1292,7 +1316,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>57</v>
       </c>
@@ -1310,7 +1334,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>58</v>
       </c>
@@ -1328,7 +1352,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>59</v>
       </c>
@@ -1346,7 +1370,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>60</v>
       </c>
@@ -1364,7 +1388,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>61</v>
       </c>
@@ -1384,46 +1408,46 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1"/>
-    <hyperlink ref="F8" r:id="rId2"/>
-    <hyperlink ref="F13" r:id="rId3"/>
-    <hyperlink ref="F14" r:id="rId4"/>
-    <hyperlink ref="F9" r:id="rId5"/>
-    <hyperlink ref="F10" r:id="rId6"/>
-    <hyperlink ref="F11" r:id="rId7"/>
-    <hyperlink ref="F15" r:id="rId8"/>
-    <hyperlink ref="F16" r:id="rId9"/>
-    <hyperlink ref="F17:F18" r:id="rId10" display="http://buildingsdatabook.eren.doe.gov/docs/xls_pdf/9.1.8.xlsx"/>
-    <hyperlink ref="F19" r:id="rId11"/>
-    <hyperlink ref="F27" r:id="rId12"/>
-    <hyperlink ref="F28:F31" r:id="rId13" display="http://buildingsdatabook.eren.doe.gov/docs/xls_pdf/9.1.13.xlsx"/>
-    <hyperlink ref="F20" r:id="rId14"/>
-    <hyperlink ref="F21" r:id="rId15"/>
-    <hyperlink ref="F25" r:id="rId16"/>
-    <hyperlink ref="F26" r:id="rId17"/>
-    <hyperlink ref="F22" r:id="rId18"/>
-    <hyperlink ref="F23" r:id="rId19"/>
-    <hyperlink ref="F24" r:id="rId20"/>
+    <hyperlink ref="F12" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="F8" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="F13" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="F14" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="F15" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="F16" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="F17:F18" r:id="rId10" display="http://buildingsdatabook.eren.doe.gov/docs/xls_pdf/9.1.8.xlsx" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="F19" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="F27" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="F28:F31" r:id="rId13" display="http://buildingsdatabook.eren.doe.gov/docs/xls_pdf/9.1.13.xlsx" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="F20" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="F21" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="F25" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="F26" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="F22" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="F23" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="F24" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1433,7 +1457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1470,7 @@
         <v>0.59781931464174454</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1459,20 +1483,20 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <f t="shared" si="0"/>
         <v>0.56609034267912772</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <f>AVERAGE(C2:C3)</f>
         <v>0.43390965732087228</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1485,7 +1509,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1498,7 +1522,7 @@
         <v>0.67017241379310344</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1521,20 +1545,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1544,7 +1568,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1557,7 +1581,7 @@
         <v>0.59781931464174454</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1570,20 +1594,20 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <f t="shared" si="0"/>
         <v>0.56609034267912772</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <f>AVERAGE(C2:C3)</f>
         <v>0.43390965732087228</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1620,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1609,7 +1633,7 @@
         <v>0.67017241379310344</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1629,20 +1653,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -1652,7 +1676,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1665,7 +1689,7 @@
         <v>0.59781931464174454</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1678,20 +1702,20 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <f t="shared" si="0"/>
         <v>0.56609034267912772</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <f>AVERAGE(C2:C3)</f>
         <v>0.43390965732087228</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1704,7 +1728,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1717,7 +1741,7 @@
         <v>0.46288946910356832</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1740,31 +1764,41 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1772,24 +1806,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1808,70 +1903,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1973,32 +2021,44 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb176f07-3112-4ee9-93fd-ae2cb5f3e433">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b15a3a4-8173-42d6-9deb-398ec38eca4b" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E91C74-9B18-45CD-8658-7A389320A66C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE63B666-BC79-4D5D-9398-4C186F7D3D0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50F7D8A9-DE15-489A-804B-F206A764DFB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0532B4A3-E156-45DB-B692-27EBB4D5CCF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A84EEE9-9EE6-47A2-9965-D121252C6269}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E22E3F9-27F6-4134-BE3B-184D9764E4ED}"/>
 </file>